--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="2715" windowWidth="13110" windowHeight="2520"/>
   </bookViews>
@@ -15,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="333">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -1051,6 +1056,10 @@
   </si>
   <si>
     <t>中债反馈消息</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资者分类*</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1321,74 +1330,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1401,14 +1342,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1443,7 +1384,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1478,7 +1419,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1714,6 +1655,7 @@
     <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
     <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
     <col min="25" max="25" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" customHeight="1">
@@ -1792,7 +1734,9 @@
       <c r="Y1" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="Z1" s="6"/>
+      <c r="Z1" s="22" t="s">
+        <v>332</v>
+      </c>
       <c r="AA1" s="6"/>
     </row>
     <row r="2" spans="1:27">
@@ -1821,7 +1765,7 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="23"/>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="6"/>
     </row>
     <row r="3" spans="1:27">
@@ -1850,7 +1794,7 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="23"/>
-      <c r="Z3" s="6"/>
+      <c r="Z3" s="13"/>
       <c r="AA3" s="6"/>
     </row>
     <row r="4" spans="1:27">
@@ -1879,7 +1823,7 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="23"/>
-      <c r="Z4" s="6"/>
+      <c r="Z4" s="13"/>
       <c r="AA4" s="6"/>
     </row>
     <row r="5" spans="1:27">
@@ -1908,7 +1852,7 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="23"/>
-      <c r="Z5" s="6"/>
+      <c r="Z5" s="13"/>
       <c r="AA5" s="6"/>
     </row>
     <row r="6" spans="1:27">
@@ -1937,7 +1881,7 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="23"/>
-      <c r="Z6" s="6"/>
+      <c r="Z6" s="13"/>
       <c r="AA6" s="6"/>
     </row>
     <row r="7" spans="1:27">
@@ -1966,7 +1910,7 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="23"/>
-      <c r="Z7" s="6"/>
+      <c r="Z7" s="13"/>
       <c r="AA7" s="6"/>
     </row>
     <row r="8" spans="1:27">
@@ -1995,7 +1939,7 @@
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="23"/>
-      <c r="Z8" s="6"/>
+      <c r="Z8" s="13"/>
       <c r="AA8" s="6"/>
     </row>
     <row r="9" spans="1:27">
@@ -2024,7 +1968,7 @@
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="23"/>
-      <c r="Z9" s="6"/>
+      <c r="Z9" s="13"/>
       <c r="AA9" s="6"/>
     </row>
     <row r="10" spans="1:27">
@@ -2053,7 +1997,7 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="23"/>
-      <c r="Z10" s="6"/>
+      <c r="Z10" s="13"/>
       <c r="AA10" s="6"/>
     </row>
     <row r="11" spans="1:27">
@@ -2082,7 +2026,7 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="23"/>
-      <c r="Z11" s="6"/>
+      <c r="Z11" s="13"/>
       <c r="AA11" s="6"/>
     </row>
     <row r="12" spans="1:27">
@@ -2111,7 +2055,7 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="23"/>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="13"/>
       <c r="AA12" s="6"/>
     </row>
     <row r="13" spans="1:27">
@@ -2140,7 +2084,7 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="23"/>
-      <c r="Z13" s="6"/>
+      <c r="Z13" s="13"/>
       <c r="AA13" s="6"/>
     </row>
     <row r="14" spans="1:27">
@@ -2169,7 +2113,7 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="23"/>
-      <c r="Z14" s="6"/>
+      <c r="Z14" s="13"/>
       <c r="AA14" s="6"/>
     </row>
     <row r="15" spans="1:27">
@@ -2198,7 +2142,7 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="23"/>
-      <c r="Z15" s="6"/>
+      <c r="Z15" s="13"/>
       <c r="AA15" s="6"/>
     </row>
     <row r="16" spans="1:27">
@@ -2227,7 +2171,7 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="23"/>
-      <c r="Z16" s="6"/>
+      <c r="Z16" s="13"/>
       <c r="AA16" s="6"/>
     </row>
     <row r="17" spans="1:27">
@@ -2256,7 +2200,7 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="23"/>
-      <c r="Z17" s="6"/>
+      <c r="Z17" s="13"/>
       <c r="AA17" s="6"/>
     </row>
     <row r="18" spans="1:27">
@@ -2285,7 +2229,7 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="23"/>
-      <c r="Z18" s="6"/>
+      <c r="Z18" s="13"/>
       <c r="AA18" s="6"/>
     </row>
     <row r="19" spans="1:27">
@@ -2314,7 +2258,7 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="23"/>
-      <c r="Z19" s="6"/>
+      <c r="Z19" s="13"/>
       <c r="AA19" s="6"/>
     </row>
     <row r="20" spans="1:27">
@@ -2343,7 +2287,7 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="23"/>
-      <c r="Z20" s="6"/>
+      <c r="Z20" s="13"/>
       <c r="AA20" s="6"/>
     </row>
     <row r="21" spans="1:27">
@@ -2372,7 +2316,7 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="23"/>
-      <c r="Z21" s="6"/>
+      <c r="Z21" s="13"/>
       <c r="AA21" s="6"/>
     </row>
     <row r="22" spans="1:27">
@@ -2401,7 +2345,7 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="23"/>
-      <c r="Z22" s="6"/>
+      <c r="Z22" s="13"/>
       <c r="AA22" s="6"/>
     </row>
     <row r="23" spans="1:27">
@@ -2430,7 +2374,7 @@
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="23"/>
-      <c r="Z23" s="6"/>
+      <c r="Z23" s="13"/>
       <c r="AA23" s="6"/>
     </row>
     <row r="24" spans="1:27">
@@ -2459,7 +2403,7 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="23"/>
-      <c r="Z24" s="6"/>
+      <c r="Z24" s="13"/>
       <c r="AA24" s="6"/>
     </row>
     <row r="25" spans="1:27">
@@ -2488,7 +2432,7 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="23"/>
-      <c r="Z25" s="6"/>
+      <c r="Z25" s="13"/>
       <c r="AA25" s="6"/>
     </row>
     <row r="26" spans="1:27">
@@ -2517,7 +2461,7 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="23"/>
-      <c r="Z26" s="6"/>
+      <c r="Z26" s="13"/>
       <c r="AA26" s="6"/>
     </row>
     <row r="27" spans="1:27">
@@ -2546,7 +2490,7 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="23"/>
-      <c r="Z27" s="6"/>
+      <c r="Z27" s="13"/>
       <c r="AA27" s="6"/>
     </row>
     <row r="28" spans="1:27">
@@ -2575,7 +2519,7 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="23"/>
-      <c r="Z28" s="6"/>
+      <c r="Z28" s="13"/>
       <c r="AA28" s="6"/>
     </row>
     <row r="29" spans="1:27">
@@ -2604,7 +2548,7 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="23"/>
-      <c r="Z29" s="6"/>
+      <c r="Z29" s="13"/>
       <c r="AA29" s="6"/>
     </row>
     <row r="30" spans="1:27">
@@ -2633,7 +2577,7 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="23"/>
-      <c r="Z30" s="6"/>
+      <c r="Z30" s="13"/>
       <c r="AA30" s="6"/>
     </row>
     <row r="31" spans="1:27">
@@ -2662,7 +2606,7 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="23"/>
-      <c r="Z31" s="6"/>
+      <c r="Z31" s="13"/>
       <c r="AA31" s="6"/>
     </row>
     <row r="32" spans="1:27">
@@ -2691,7 +2635,7 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="23"/>
-      <c r="Z32" s="6"/>
+      <c r="Z32" s="13"/>
       <c r="AA32" s="6"/>
     </row>
     <row r="33" spans="1:27">
@@ -2720,7 +2664,7 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="23"/>
-      <c r="Z33" s="6"/>
+      <c r="Z33" s="13"/>
       <c r="AA33" s="6"/>
     </row>
     <row r="34" spans="1:27">
@@ -2749,12 +2693,12 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="23"/>
-      <c r="Z34" s="6"/>
+      <c r="Z34" s="13"/>
       <c r="AA34" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
@@ -2772,6 +2716,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z1:Z1048576">
+      <formula1>"02 合格投资者,01 不特定社会公众"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
@@ -1628,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
@@ -1653,12 +1653,12 @@
     <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
     <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
     <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
-    <col min="23" max="24" width="18.25" style="11" customWidth="1"/>
-    <col min="25" max="25" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19" style="10" customWidth="1"/>
+    <col min="23" max="23" width="19" style="10" customWidth="1"/>
+    <col min="24" max="25" width="18.25" style="11" customWidth="1"/>
+    <col min="26" max="26" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" customHeight="1">
+    <row r="1" spans="1:26" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1725,21 +1725,20 @@
       <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="X1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="Z1" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA1" s="6"/>
-    </row>
-    <row r="2" spans="1:27">
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="13"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1764,11 +1763,10 @@
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="6"/>
-    </row>
-    <row r="3" spans="1:27">
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="23"/>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1793,11 +1791,10 @@
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="6"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="23"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1822,11 +1819,10 @@
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="6"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="23"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1851,11 +1847,10 @@
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="6"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="23"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1880,11 +1875,10 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="6"/>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="23"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1909,11 +1903,10 @@
       <c r="V7" s="13"/>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="6"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="23"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1938,11 +1931,10 @@
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="6"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="23"/>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1967,11 +1959,10 @@
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="6"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="23"/>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1996,11 +1987,10 @@
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="6"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2025,11 +2015,10 @@
       <c r="V11" s="13"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="6"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="23"/>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2054,11 +2043,10 @@
       <c r="V12" s="13"/>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="6"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2083,11 +2071,10 @@
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="6"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="23"/>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2112,11 +2099,10 @@
       <c r="V14" s="13"/>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="6"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2141,11 +2127,10 @@
       <c r="V15" s="13"/>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="6"/>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="23"/>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2170,11 +2155,10 @@
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="6"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="23"/>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2199,11 +2183,10 @@
       <c r="V17" s="13"/>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="6"/>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="23"/>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2228,11 +2211,10 @@
       <c r="V18" s="13"/>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="6"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="23"/>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2257,11 +2239,10 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="6"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2286,11 +2267,10 @@
       <c r="V20" s="13"/>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="6"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="23"/>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2315,11 +2295,10 @@
       <c r="V21" s="13"/>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="6"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="23"/>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2344,11 +2323,10 @@
       <c r="V22" s="13"/>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="6"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="23"/>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2373,11 +2351,10 @@
       <c r="V23" s="13"/>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="6"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="23"/>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2402,11 +2379,10 @@
       <c r="V24" s="13"/>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="6"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="23"/>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2431,11 +2407,10 @@
       <c r="V25" s="13"/>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="6"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="23"/>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2460,11 +2435,10 @@
       <c r="V26" s="13"/>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="6"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="23"/>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2489,11 +2463,10 @@
       <c r="V27" s="13"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="6"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="23"/>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2518,11 +2491,10 @@
       <c r="V28" s="13"/>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="6"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="23"/>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2547,11 +2519,10 @@
       <c r="V29" s="13"/>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="6"/>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="23"/>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2576,11 +2547,10 @@
       <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="13"/>
-      <c r="AA30" s="6"/>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="23"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2605,11 +2575,10 @@
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="6"/>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="23"/>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2634,11 +2603,10 @@
       <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="13"/>
-      <c r="AA32" s="6"/>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="23"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2663,11 +2631,10 @@
       <c r="V33" s="13"/>
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="6"/>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="23"/>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2692,9 +2659,8 @@
       <c r="V34" s="13"/>
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="13"/>
-      <c r="AA34" s="6"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -2717,7 +2683,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576">
       <formula1>"01 保守型,02 稳健型,03 平衡型,04 成长型,05 进取型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z1:Z1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1:W1048576">
       <formula1>"02 合格投资者,01 不特定社会公众"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/EquityInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\3.0.1\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="13110" windowHeight="2520"/>
+    <workbookView xWindow="0" yWindow="2720" windowWidth="13110" windowHeight="2520"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息维护模板" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="375">
   <si>
     <t>登记银行代码*</t>
   </si>
@@ -1061,6 +1061,134 @@
   <si>
     <t>投资者分类*</t>
     <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号开户所在地</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>中债销售区域</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>110000 北京市</t>
+  </si>
+  <si>
+    <t>120000 天津市</t>
+  </si>
+  <si>
+    <t>130000 河北省</t>
+  </si>
+  <si>
+    <t>140000 山西省</t>
+  </si>
+  <si>
+    <t>150000 内蒙古自治区</t>
+  </si>
+  <si>
+    <t>210000 辽宁省</t>
+  </si>
+  <si>
+    <t>210200 大连市</t>
+  </si>
+  <si>
+    <t>220000 吉林省</t>
+  </si>
+  <si>
+    <t>230000 黑龙江省</t>
+  </si>
+  <si>
+    <t>310000 上海市</t>
+  </si>
+  <si>
+    <t>320000 江苏省</t>
+  </si>
+  <si>
+    <t>330000 浙江省</t>
+  </si>
+  <si>
+    <t>330200 宁波市</t>
+  </si>
+  <si>
+    <t>340000 安徽省</t>
+  </si>
+  <si>
+    <t>350000 福建省</t>
+  </si>
+  <si>
+    <t>350200 厦门市</t>
+  </si>
+  <si>
+    <t>360000 江西省</t>
+  </si>
+  <si>
+    <t>370000 山东省</t>
+  </si>
+  <si>
+    <t>370200 青岛市</t>
+  </si>
+  <si>
+    <t>410000 河南省</t>
+  </si>
+  <si>
+    <t>420000 湖北省</t>
+  </si>
+  <si>
+    <t>430000 湖南省</t>
+  </si>
+  <si>
+    <t>440000 广东省</t>
+  </si>
+  <si>
+    <t>440300 深圳市</t>
+  </si>
+  <si>
+    <t>450000 广西壮族自治区</t>
+  </si>
+  <si>
+    <t>460000 海南省</t>
+  </si>
+  <si>
+    <t>500000 重庆市</t>
+  </si>
+  <si>
+    <t>510000 四川省</t>
+  </si>
+  <si>
+    <t>520000 贵州省</t>
+  </si>
+  <si>
+    <t>530000 云南省</t>
+  </si>
+  <si>
+    <t>540000 西藏自治区</t>
+  </si>
+  <si>
+    <t>610000 陕西省</t>
+  </si>
+  <si>
+    <t>620000 甘肃省</t>
+  </si>
+  <si>
+    <t>630000 青海省</t>
+  </si>
+  <si>
+    <t>640000 宁夏回族自治区</t>
+  </si>
+  <si>
+    <t>650000 新疆维吾尔自治区</t>
+  </si>
+  <si>
+    <t>710000 台湾</t>
+  </si>
+  <si>
+    <t>810000 香港</t>
+  </si>
+  <si>
+    <t>820000 澳门</t>
+  </si>
+  <si>
+    <t>900000 其他国家或地区</t>
   </si>
 </sst>
 </file>
@@ -1628,37 +1756,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AA34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="10" customWidth="1"/>
-    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="10" customWidth="1"/>
-    <col min="5" max="5" width="27.625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.25" style="10" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="27.6328125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" style="10" customWidth="1"/>
     <col min="9" max="9" width="19" style="10" customWidth="1"/>
-    <col min="10" max="10" width="14.125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="31.625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="24.75" style="10" customWidth="1"/>
-    <col min="13" max="13" width="22.75" style="10" customWidth="1"/>
-    <col min="14" max="14" width="23.25" style="10" customWidth="1"/>
-    <col min="15" max="15" width="23.375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.25" style="10" customWidth="1"/>
-    <col min="17" max="17" width="8.875" style="10" customWidth="1"/>
-    <col min="18" max="18" width="10.875" style="10" customWidth="1"/>
-    <col min="19" max="19" width="12.75" style="10" customWidth="1"/>
-    <col min="20" max="20" width="13.25" style="10" customWidth="1"/>
-    <col min="21" max="21" width="16.375" style="10" customWidth="1"/>
-    <col min="22" max="22" width="12.5" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" style="10" customWidth="1"/>
+    <col min="11" max="11" width="31.6328125" style="10" customWidth="1"/>
+    <col min="12" max="12" width="24.7265625" style="10" customWidth="1"/>
+    <col min="13" max="13" width="22.7265625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="23.26953125" style="10" customWidth="1"/>
+    <col min="15" max="15" width="23.36328125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23.26953125" style="10" customWidth="1"/>
+    <col min="17" max="17" width="8.90625" style="10" customWidth="1"/>
+    <col min="18" max="18" width="10.90625" style="10" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" style="10" customWidth="1"/>
+    <col min="20" max="20" width="13.26953125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16.36328125" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.453125" style="11" customWidth="1"/>
     <col min="23" max="23" width="19" style="10" customWidth="1"/>
-    <col min="24" max="25" width="18.25" style="11" customWidth="1"/>
-    <col min="26" max="26" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="18.26953125" style="11" customWidth="1"/>
+    <col min="27" max="27" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="21" customHeight="1">
+    <row r="1" spans="1:27" ht="21" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1729,16 +1857,19 @@
         <v>332</v>
       </c>
       <c r="X1" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" s="13"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -1764,9 +1895,10 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
-      <c r="Z2" s="23"/>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="23"/>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1792,9 +1924,10 @@
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
-      <c r="Z3" s="23"/>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="23"/>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1820,9 +1953,10 @@
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
-      <c r="Z4" s="23"/>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="23"/>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1848,9 +1982,10 @@
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
-      <c r="Z5" s="23"/>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="23"/>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1876,9 +2011,10 @@
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
-      <c r="Z6" s="23"/>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="23"/>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1904,9 +2040,10 @@
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
-      <c r="Z7" s="23"/>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="23"/>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1932,9 +2069,10 @@
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
-      <c r="Z8" s="23"/>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="23"/>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1960,9 +2098,10 @@
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
-      <c r="Z9" s="23"/>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="23"/>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1988,9 +2127,10 @@
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
-      <c r="Z10" s="23"/>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="23"/>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2016,9 +2156,10 @@
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
-      <c r="Z11" s="23"/>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="23"/>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2044,9 +2185,10 @@
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
-      <c r="Z12" s="23"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="23"/>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2072,9 +2214,10 @@
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
-      <c r="Z13" s="23"/>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="23"/>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2100,9 +2243,10 @@
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
-      <c r="Z14" s="23"/>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="23"/>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2128,9 +2272,10 @@
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
-      <c r="Z15" s="23"/>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="23"/>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2156,9 +2301,10 @@
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
-      <c r="Z16" s="23"/>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="23"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2184,9 +2330,10 @@
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
-      <c r="Z17" s="23"/>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="23"/>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2212,9 +2359,10 @@
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
-      <c r="Z18" s="23"/>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="23"/>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2240,9 +2388,10 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
-      <c r="Z19" s="23"/>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="23"/>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2268,9 +2417,10 @@
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
-      <c r="Z20" s="23"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="23"/>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -2296,9 +2446,10 @@
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
-      <c r="Z21" s="23"/>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="23"/>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -2324,9 +2475,10 @@
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
-      <c r="Z22" s="23"/>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="23"/>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -2352,9 +2504,10 @@
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
-      <c r="Z23" s="23"/>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="23"/>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -2380,9 +2533,10 @@
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
-      <c r="Z24" s="23"/>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="23"/>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -2408,9 +2562,10 @@
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
-      <c r="Z25" s="23"/>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="23"/>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -2436,9 +2591,10 @@
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
-      <c r="Z26" s="23"/>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="23"/>
+    </row>
+    <row r="27" spans="1:27">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -2464,9 +2620,10 @@
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
-      <c r="Z27" s="23"/>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="23"/>
+    </row>
+    <row r="28" spans="1:27">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -2492,9 +2649,10 @@
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
       <c r="Y28" s="13"/>
-      <c r="Z28" s="23"/>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="23"/>
+    </row>
+    <row r="29" spans="1:27">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -2520,9 +2678,10 @@
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="13"/>
-      <c r="Z29" s="23"/>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="23"/>
+    </row>
+    <row r="30" spans="1:27">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -2548,9 +2707,10 @@
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
       <c r="Y30" s="13"/>
-      <c r="Z30" s="23"/>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="23"/>
+    </row>
+    <row r="31" spans="1:27">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -2576,9 +2736,10 @@
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="13"/>
-      <c r="Z31" s="23"/>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="23"/>
+    </row>
+    <row r="32" spans="1:27">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2604,9 +2765,10 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="13"/>
-      <c r="Z32" s="23"/>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="23"/>
+    </row>
+    <row r="33" spans="1:27">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2632,9 +2794,10 @@
       <c r="W33" s="13"/>
       <c r="X33" s="13"/>
       <c r="Y33" s="13"/>
-      <c r="Z33" s="23"/>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="23"/>
+    </row>
+    <row r="34" spans="1:27">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2660,7 +2823,8 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="13"/>
-      <c r="Z34" s="23"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -2688,15 +2852,21 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$36:$A$70</xm:f>
           </x14:formula1>
           <xm:sqref>K1:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$316:$A$355</xm:f>
+          </x14:formula1>
+          <xm:sqref>X1:X1048576 X1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2706,10 +2876,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A311"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:A355"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="100.75" customWidth="1"/>
+    <col min="1" max="1" width="100.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="33.75" customHeight="1">
@@ -4256,6 +4426,211 @@
     <row r="311" spans="1:1">
       <c r="A311" s="9" t="s">
         <v>329</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
